--- a/Team-Data/2014-15/3-22-2014-15.xlsx
+++ b/Team-Data/2014-15/3-22-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E2" t="n">
         <v>53</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.757</v>
+        <v>0.768</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -688,37 +755,37 @@
         <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="N2" t="n">
-        <v>0.386</v>
+        <v>0.384</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P2" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="R2" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T2" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="U2" t="n">
         <v>25.4</v>
       </c>
       <c r="V2" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W2" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X2" t="n">
         <v>4.7</v>
@@ -727,19 +794,19 @@
         <v>4.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.6</v>
+        <v>102.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -751,10 +818,10 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ2" t="n">
         <v>27</v>
@@ -763,7 +830,7 @@
         <v>4</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
         <v>7</v>
@@ -775,7 +842,7 @@
         <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
         <v>4</v>
@@ -784,22 +851,22 @@
         <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
         <v>17</v>
@@ -808,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB2" t="n">
         <v>9</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -843,55 +910,55 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" t="n">
         <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>0.435</v>
+        <v>0.441</v>
       </c>
       <c r="H3" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J3" t="n">
-        <v>88.3</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L3" t="n">
         <v>8.1</v>
       </c>
       <c r="M3" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.331</v>
+        <v>0.332</v>
       </c>
       <c r="O3" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="P3" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R3" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S3" t="n">
-        <v>32.8</v>
+        <v>32.6</v>
       </c>
       <c r="T3" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="U3" t="n">
         <v>24.3</v>
@@ -903,37 +970,37 @@
         <v>8</v>
       </c>
       <c r="X3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z3" t="n">
         <v>21.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.7</v>
+        <v>100.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
         <v>19</v>
       </c>
       <c r="AF3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI3" t="n">
         <v>5</v>
@@ -942,10 +1009,10 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM3" t="n">
         <v>12</v>
@@ -966,10 +1033,10 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
@@ -981,13 +1048,13 @@
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>29</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-3.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
         <v>22</v>
@@ -1142,19 +1209,19 @@
         <v>17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR4" t="n">
         <v>23</v>
       </c>
       <c r="AS4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
         <v>23</v>
       </c>
       <c r="AU4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV4" t="n">
         <v>16</v>
@@ -1166,13 +1233,13 @@
         <v>25</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" t="n">
         <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>0.441</v>
+        <v>0.433</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J5" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.425</v>
+        <v>0.424</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
@@ -1243,13 +1310,13 @@
         <v>17.2</v>
       </c>
       <c r="P5" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S5" t="n">
         <v>34</v>
@@ -1261,40 +1328,40 @@
         <v>20.5</v>
       </c>
       <c r="V5" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="W5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="X5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z5" t="n">
         <v>18.5</v>
       </c>
       <c r="AA5" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE5" t="n">
         <v>21</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>19</v>
       </c>
       <c r="AF5" t="n">
         <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
         <v>8</v>
@@ -1312,7 +1379,7 @@
         <v>27</v>
       </c>
       <c r="AM5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN5" t="n">
         <v>30</v>
@@ -1321,7 +1388,7 @@
         <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ5" t="n">
         <v>19</v>
@@ -1330,10 +1397,10 @@
         <v>25</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
         <v>25</v>
@@ -1357,7 +1424,7 @@
         <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC5" t="n">
         <v>22</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>10</v>
@@ -1479,16 +1546,16 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI6" t="n">
         <v>23</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
         <v>14</v>
@@ -1506,19 +1573,19 @@
         <v>3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR6" t="n">
         <v>5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
         <v>3</v>
       </c>
       <c r="AU6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV6" t="n">
         <v>14</v>
@@ -1527,7 +1594,7 @@
         <v>29</v>
       </c>
       <c r="AX6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="n">
         <v>23</v>
@@ -1536,7 +1603,7 @@
         <v>3</v>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
         <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>0.639</v>
+        <v>0.634</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
@@ -1592,25 +1659,25 @@
         <v>82.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O7" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P7" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R7" t="n">
         <v>11.1</v>
@@ -1619,7 +1686,7 @@
         <v>31.7</v>
       </c>
       <c r="T7" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U7" t="n">
         <v>21.9</v>
@@ -1628,31 +1695,31 @@
         <v>13.9</v>
       </c>
       <c r="W7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X7" t="n">
         <v>4.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB7" t="n">
         <v>103.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF7" t="n">
         <v>8</v>
@@ -1661,22 +1728,22 @@
         <v>7</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>14</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
       </c>
       <c r="AM7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
         <v>6</v>
@@ -1703,16 +1770,16 @@
         <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
       </c>
       <c r="AY7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ7" t="n">
         <v>5</v>
@@ -1724,7 +1791,7 @@
         <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -1771,19 +1838,19 @@
         <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.46</v>
+        <v>0.462</v>
       </c>
       <c r="L8" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.353</v>
+        <v>0.355</v>
       </c>
       <c r="O8" t="n">
         <v>16.7</v>
@@ -1792,28 +1859,28 @@
         <v>22.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.753</v>
+        <v>0.756</v>
       </c>
       <c r="R8" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
         <v>22.5</v>
       </c>
       <c r="V8" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y8" t="n">
         <v>3.8</v>
@@ -1822,16 +1889,16 @@
         <v>19.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.7</v>
+        <v>104.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1852,7 +1919,7 @@
         <v>9</v>
       </c>
       <c r="AK8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL8" t="n">
         <v>7</v>
@@ -1867,16 +1934,16 @@
         <v>18</v>
       </c>
       <c r="AP8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ8" t="n">
         <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT8" t="n">
         <v>24</v>
@@ -1885,10 +1952,10 @@
         <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX8" t="n">
         <v>16</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" t="n">
         <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>0.38</v>
+        <v>0.371</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1953,7 +2020,7 @@
         <v>37.4</v>
       </c>
       <c r="J9" t="n">
-        <v>86.8</v>
+        <v>86.7</v>
       </c>
       <c r="K9" t="n">
         <v>0.431</v>
@@ -1965,7 +2032,7 @@
         <v>24.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.321</v>
+        <v>0.319</v>
       </c>
       <c r="O9" t="n">
         <v>17.7</v>
@@ -1977,16 +2044,16 @@
         <v>0.729</v>
       </c>
       <c r="R9" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S9" t="n">
         <v>32.6</v>
       </c>
       <c r="T9" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U9" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V9" t="n">
         <v>14.1</v>
@@ -1998,22 +2065,22 @@
         <v>4.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z9" t="n">
         <v>22.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>100.5</v>
+        <v>100.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.4</v>
+        <v>-3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2025,7 +2092,7 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
         <v>17</v>
@@ -2046,34 +2113,34 @@
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
         <v>24</v>
       </c>
       <c r="AR9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV9" t="n">
         <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY9" t="n">
         <v>30</v>
@@ -2082,7 +2149,7 @@
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB9" t="n">
         <v>15</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -2117,22 +2184,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
         <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>0.371</v>
+        <v>0.362</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J10" t="n">
         <v>86.2</v>
@@ -2147,25 +2214,25 @@
         <v>25.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.336</v>
+        <v>0.335</v>
       </c>
       <c r="O10" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.707</v>
+        <v>0.709</v>
       </c>
       <c r="R10" t="n">
         <v>13</v>
       </c>
       <c r="S10" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="T10" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="U10" t="n">
         <v>21.2</v>
@@ -2174,10 +2241,10 @@
         <v>13.5</v>
       </c>
       <c r="W10" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y10" t="n">
         <v>5</v>
@@ -2189,13 +2256,13 @@
         <v>19.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,13 +2274,13 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
         <v>28</v>
@@ -2240,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
         <v>4</v>
@@ -2255,7 +2322,7 @@
         <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
@@ -2264,7 +2331,7 @@
         <v>8</v>
       </c>
       <c r="BA10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>10.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2389,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
@@ -2404,7 +2471,7 @@
         <v>2</v>
       </c>
       <c r="AM11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
@@ -2413,7 +2480,7 @@
         <v>22</v>
       </c>
       <c r="AP11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ11" t="n">
         <v>8</v>
@@ -2425,7 +2492,7 @@
         <v>4</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F12" t="n">
         <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>0.662</v>
+        <v>0.667</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,7 +2566,7 @@
         <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>84.3</v>
+        <v>84.2</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
@@ -2511,58 +2578,58 @@
         <v>33.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
-        <v>17.6</v>
+        <v>17.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="R12" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S12" t="n">
         <v>31.8</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U12" t="n">
         <v>22.2</v>
       </c>
       <c r="V12" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="W12" t="n">
         <v>9.5</v>
       </c>
       <c r="X12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y12" t="n">
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.2</v>
+        <v>103.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>4</v>
@@ -2571,13 +2638,13 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>20</v>
       </c>
       <c r="AJ12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2589,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
@@ -2607,13 +2674,13 @@
         <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
         <v>9</v>
       </c>
       <c r="AV12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW12" t="n">
         <v>3</v>
@@ -2628,13 +2695,13 @@
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
         <v>8</v>
       </c>
       <c r="BC12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -2741,31 +2808,31 @@
         <v>-0.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
         <v>19</v>
       </c>
       <c r="AF13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG13" t="n">
         <v>20</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK13" t="n">
         <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
@@ -2795,19 +2862,19 @@
         <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
         <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY13" t="n">
         <v>16</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
         <v>7</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" t="n">
         <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>0.648</v>
+        <v>0.643</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2863,7 +2930,7 @@
         <v>39.3</v>
       </c>
       <c r="J14" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.471</v>
@@ -2872,10 +2939,10 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="O14" t="n">
         <v>17.6</v>
@@ -2890,7 +2957,7 @@
         <v>9.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T14" t="n">
         <v>42.2</v>
@@ -2908,7 +2975,7 @@
         <v>4.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Z14" t="n">
         <v>21.4</v>
@@ -2923,16 +2990,16 @@
         <v>5.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
       </c>
       <c r="AG14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH14" t="n">
         <v>29</v>
@@ -2941,13 +3008,13 @@
         <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM14" t="n">
         <v>5</v>
@@ -2959,7 +3026,7 @@
         <v>11</v>
       </c>
       <c r="AP14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
         <v>28</v>
@@ -2968,7 +3035,7 @@
         <v>28</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
         <v>21</v>
@@ -2983,7 +3050,7 @@
         <v>14</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -3030,28 +3097,28 @@
         <v>67</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>0.269</v>
+        <v>0.254</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
         <v>18.8</v>
@@ -3060,22 +3127,22 @@
         <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="T15" t="n">
-        <v>44.4</v>
+        <v>44.1</v>
       </c>
       <c r="U15" t="n">
         <v>20.9</v>
@@ -3087,31 +3154,31 @@
         <v>7.3</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
@@ -3120,7 +3187,7 @@
         <v>5</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
         <v>7</v>
@@ -3141,19 +3208,19 @@
         <v>12</v>
       </c>
       <c r="AP15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS15" t="n">
         <v>13</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR15" t="n">
+      <c r="AT15" t="n">
         <v>9</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8</v>
       </c>
       <c r="AU15" t="n">
         <v>20</v>
@@ -3162,25 +3229,25 @@
         <v>5</v>
       </c>
       <c r="AW15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX15" t="n">
         <v>21</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>19</v>
       </c>
       <c r="AY15" t="n">
         <v>15</v>
       </c>
       <c r="AZ15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA15" t="n">
         <v>22</v>
       </c>
-      <c r="BA15" t="n">
-        <v>23</v>
-      </c>
       <c r="BB15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3317,22 +3384,22 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
         <v>7</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
         <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT16" t="n">
         <v>20</v>
@@ -3350,7 +3417,7 @@
         <v>24</v>
       </c>
       <c r="AY16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>9</v>
@@ -3362,7 +3429,7 @@
         <v>17</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E17" t="n">
         <v>32</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" t="n">
-        <v>0.464</v>
+        <v>0.471</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
@@ -3409,10 +3476,10 @@
         <v>35.1</v>
       </c>
       <c r="J17" t="n">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L17" t="n">
         <v>6.9</v>
@@ -3421,19 +3488,19 @@
         <v>20.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="O17" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P17" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.741</v>
+        <v>0.743</v>
       </c>
       <c r="R17" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S17" t="n">
         <v>30</v>
@@ -3442,7 +3509,7 @@
         <v>38.8</v>
       </c>
       <c r="U17" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V17" t="n">
         <v>14.8</v>
@@ -3454,22 +3521,22 @@
         <v>4.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA17" t="n">
         <v>20.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,10 +3557,10 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="n">
         <v>19</v>
@@ -3508,7 +3575,7 @@
         <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3532,10 +3599,10 @@
         <v>23</v>
       </c>
       <c r="AY17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
         <v>8</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18" t="n">
         <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>0.486</v>
+        <v>0.493</v>
       </c>
       <c r="H18" t="n">
         <v>48.7</v>
@@ -3591,25 +3658,25 @@
         <v>37.4</v>
       </c>
       <c r="J18" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L18" t="n">
         <v>6.8</v>
       </c>
       <c r="M18" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O18" t="n">
         <v>16.2</v>
       </c>
       <c r="P18" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q18" t="n">
         <v>0.768</v>
@@ -3621,13 +3688,13 @@
         <v>31.7</v>
       </c>
       <c r="T18" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U18" t="n">
         <v>23.2</v>
       </c>
       <c r="V18" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="W18" t="n">
         <v>9.4</v>
@@ -3636,22 +3703,22 @@
         <v>4.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3666,10 +3733,10 @@
         <v>3</v>
       </c>
       <c r="AI18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK18" t="n">
         <v>10</v>
@@ -3678,7 +3745,7 @@
         <v>23</v>
       </c>
       <c r="AM18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN18" t="n">
         <v>4</v>
@@ -3687,16 +3754,16 @@
         <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ18" t="n">
         <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT18" t="n">
         <v>22</v>
@@ -3705,16 +3772,16 @@
         <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW18" t="n">
         <v>4</v>
       </c>
       <c r="AX18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E19" t="n">
         <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
-        <v>0.217</v>
+        <v>0.221</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,10 +3840,10 @@
         <v>36.7</v>
       </c>
       <c r="J19" t="n">
-        <v>84.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L19" t="n">
         <v>4.9</v>
@@ -3785,28 +3852,28 @@
         <v>14.7</v>
       </c>
       <c r="N19" t="n">
-        <v>0.331</v>
+        <v>0.33</v>
       </c>
       <c r="O19" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="P19" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q19" t="n">
         <v>0.767</v>
       </c>
       <c r="R19" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S19" t="n">
         <v>29.7</v>
       </c>
       <c r="T19" t="n">
-        <v>41.7</v>
+        <v>41.9</v>
       </c>
       <c r="U19" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V19" t="n">
         <v>15</v>
@@ -3815,25 +3882,25 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="n">
         <v>5.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB19" t="n">
         <v>97.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-8.1</v>
+        <v>-8</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3851,7 +3918,7 @@
         <v>22</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3866,7 +3933,7 @@
         <v>26</v>
       </c>
       <c r="AO19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP19" t="n">
         <v>2</v>
@@ -3875,7 +3942,7 @@
         <v>11</v>
       </c>
       <c r="AR19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
         <v>30</v>
@@ -3890,7 +3957,7 @@
         <v>24</v>
       </c>
       <c r="AW19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX19" t="n">
         <v>27</v>
@@ -3902,7 +3969,7 @@
         <v>10</v>
       </c>
       <c r="BA19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -3940,13 +4007,13 @@
         <v>69</v>
       </c>
       <c r="E20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G20" t="n">
-        <v>0.522</v>
+        <v>0.536</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,49 +4022,49 @@
         <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>82.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.455</v>
       </c>
       <c r="L20" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.366</v>
+        <v>0.361</v>
       </c>
       <c r="O20" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P20" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.768</v>
+        <v>0.763</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="S20" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T20" t="n">
-        <v>43.5</v>
+        <v>43.8</v>
       </c>
       <c r="U20" t="n">
         <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W20" t="n">
         <v>6.7</v>
       </c>
       <c r="X20" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="Y20" t="n">
         <v>5.9</v>
@@ -4006,25 +4073,25 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
         <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
         <v>21</v>
@@ -4033,37 +4100,37 @@
         <v>13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM20" t="n">
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
         <v>19</v>
       </c>
       <c r="AP20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR20" t="n">
         <v>9</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>10</v>
       </c>
       <c r="AS20" t="n">
         <v>17</v>
       </c>
       <c r="AT20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E21" t="n">
         <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2</v>
+        <v>0.203</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
@@ -4137,7 +4204,7 @@
         <v>35.4</v>
       </c>
       <c r="J21" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0.429</v>
@@ -4149,28 +4216,28 @@
         <v>19.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.348</v>
+        <v>0.347</v>
       </c>
       <c r="O21" t="n">
         <v>14.6</v>
       </c>
       <c r="P21" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.764</v>
+        <v>0.765</v>
       </c>
       <c r="R21" t="n">
         <v>10.8</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T21" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="U21" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V21" t="n">
         <v>14.3</v>
@@ -4179,7 +4246,7 @@
         <v>7.1</v>
       </c>
       <c r="X21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y21" t="n">
         <v>4.3</v>
@@ -4191,13 +4258,13 @@
         <v>19.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>92.2</v>
+        <v>92.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-9</v>
+        <v>-8.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4209,7 +4276,7 @@
         <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI21" t="n">
         <v>27</v>
@@ -4221,13 +4288,13 @@
         <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
@@ -4245,19 +4312,19 @@
         <v>29</v>
       </c>
       <c r="AT21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU21" t="n">
         <v>18</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW21" t="n">
         <v>23</v>
       </c>
       <c r="AX21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY21" t="n">
         <v>8</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F22" t="n">
         <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>0.571</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4328,37 +4395,37 @@
         <v>7.5</v>
       </c>
       <c r="M22" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="N22" t="n">
         <v>0.333</v>
       </c>
       <c r="O22" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="P22" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="R22" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S22" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="T22" t="n">
-        <v>47.7</v>
+        <v>47.6</v>
       </c>
       <c r="U22" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V22" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W22" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X22" t="n">
         <v>5.9</v>
@@ -4367,37 +4434,37 @@
         <v>4.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>103.2</v>
+        <v>103.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH22" t="n">
         <v>13</v>
       </c>
       <c r="AI22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK22" t="n">
         <v>19</v>
@@ -4415,10 +4482,10 @@
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4436,25 +4503,25 @@
         <v>22</v>
       </c>
       <c r="AW22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
         <v>29</v>
       </c>
       <c r="BA22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB22" t="n">
         <v>7</v>
       </c>
       <c r="BC22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -4498,22 +4565,22 @@
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J23" t="n">
         <v>82.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
         <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.353</v>
+        <v>0.355</v>
       </c>
       <c r="O23" t="n">
         <v>14.2</v>
@@ -4522,19 +4589,19 @@
         <v>19.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.728</v>
+        <v>0.727</v>
       </c>
       <c r="R23" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>41.1</v>
+        <v>41.4</v>
       </c>
       <c r="U23" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V23" t="n">
         <v>14.8</v>
@@ -4543,25 +4610,25 @@
         <v>7.9</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>21.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.3</v>
+        <v>96</v>
       </c>
       <c r="AC23" t="n">
         <v>-5.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4606,13 +4673,13 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
         <v>27</v>
       </c>
       <c r="AU23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AV23" t="n">
         <v>21</v>
@@ -4621,13 +4688,13 @@
         <v>13</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4636,7 +4703,7 @@
         <v>25</v>
       </c>
       <c r="BC23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E24" t="n">
         <v>17</v>
       </c>
       <c r="F24" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G24" t="n">
-        <v>0.243</v>
+        <v>0.246</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="J24" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.408</v>
+        <v>0.409</v>
       </c>
       <c r="L24" t="n">
         <v>8.1</v>
@@ -4701,7 +4768,7 @@
         <v>16</v>
       </c>
       <c r="P24" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q24" t="n">
         <v>0.674</v>
@@ -4710,7 +4777,7 @@
         <v>11.7</v>
       </c>
       <c r="S24" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T24" t="n">
         <v>43</v>
@@ -4719,16 +4786,16 @@
         <v>20.7</v>
       </c>
       <c r="V24" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="W24" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X24" t="n">
         <v>6.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z24" t="n">
         <v>21.3</v>
@@ -4737,16 +4804,16 @@
         <v>20.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>91</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF24" t="n">
         <v>28</v>
@@ -4755,19 +4822,19 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM24" t="n">
         <v>9</v>
@@ -4776,7 +4843,7 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP24" t="n">
         <v>11</v>
@@ -4803,13 +4870,13 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
         <v>26</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
         <v>18</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E25" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F25" t="n">
         <v>33</v>
       </c>
       <c r="G25" t="n">
-        <v>0.535</v>
+        <v>0.529</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
@@ -4865,19 +4932,19 @@
         <v>39.3</v>
       </c>
       <c r="J25" t="n">
-        <v>86.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L25" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="M25" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O25" t="n">
         <v>16.7</v>
@@ -4886,22 +4953,22 @@
         <v>21.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="R25" t="n">
         <v>11.1</v>
       </c>
       <c r="S25" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T25" t="n">
         <v>43.5</v>
       </c>
       <c r="U25" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V25" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W25" t="n">
         <v>8.699999999999999</v>
@@ -4919,22 +4986,22 @@
         <v>20.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.2</v>
+        <v>104.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
       </c>
       <c r="AF25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH25" t="n">
         <v>6</v>
@@ -4943,10 +5010,10 @@
         <v>3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL25" t="n">
         <v>8</v>
@@ -4961,16 +5028,16 @@
         <v>17</v>
       </c>
       <c r="AP25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR25" t="n">
         <v>12</v>
       </c>
       <c r="AS25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT25" t="n">
         <v>16</v>
@@ -4997,7 +5064,7 @@
         <v>12</v>
       </c>
       <c r="BB25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC25" t="n">
         <v>14</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5116,10 +5183,10 @@
         <v>5</v>
       </c>
       <c r="AG26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
         <v>9</v>
@@ -5131,7 +5198,7 @@
         <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM26" t="n">
         <v>2</v>
@@ -5164,7 +5231,7 @@
         <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX26" t="n">
         <v>15</v>
@@ -5182,7 +5249,7 @@
         <v>10</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F27" t="n">
         <v>45</v>
       </c>
       <c r="G27" t="n">
-        <v>0.348</v>
+        <v>0.338</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
@@ -5232,7 +5299,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L27" t="n">
         <v>5.4</v>
@@ -5241,25 +5308,25 @@
         <v>16.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.335</v>
+        <v>0.333</v>
       </c>
       <c r="O27" t="n">
         <v>22.9</v>
       </c>
       <c r="P27" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R27" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S27" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="T27" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U27" t="n">
         <v>19.9</v>
@@ -5268,7 +5335,7 @@
         <v>16.6</v>
       </c>
       <c r="W27" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X27" t="n">
         <v>3.8</v>
@@ -5277,19 +5344,19 @@
         <v>6.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.1</v>
+        <v>101</v>
       </c>
       <c r="AC27" t="n">
-        <v>-3.9</v>
+        <v>-4.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,7 +5368,7 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5337,7 +5404,7 @@
         <v>8</v>
       </c>
       <c r="AT27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5346,7 +5413,7 @@
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX27" t="n">
         <v>28</v>
@@ -5355,7 +5422,7 @@
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -5408,43 +5475,43 @@
         <v>48.8</v>
       </c>
       <c r="I28" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.362</v>
+        <v>0.364</v>
       </c>
       <c r="O28" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P28" t="n">
         <v>22.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U28" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="V28" t="n">
         <v>13.9</v>
@@ -5459,19 +5526,19 @@
         <v>4.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.6</v>
+        <v>102.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
         <v>9</v>
@@ -5486,13 +5553,13 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK28" t="n">
         <v>6</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>5</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,13 +5568,13 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ28" t="n">
         <v>7</v>
@@ -5525,7 +5592,7 @@
         <v>5</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
         <v>12</v>
@@ -5546,7 +5613,7 @@
         <v>11</v>
       </c>
       <c r="BC28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E29" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F29" t="n">
         <v>28</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6</v>
+        <v>0.594</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5593,22 +5660,22 @@
         <v>38</v>
       </c>
       <c r="J29" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M29" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="N29" t="n">
         <v>0.351</v>
       </c>
       <c r="O29" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P29" t="n">
         <v>24.8</v>
@@ -5620,7 +5687,7 @@
         <v>10.8</v>
       </c>
       <c r="S29" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="T29" t="n">
         <v>41.5</v>
@@ -5629,10 +5696,10 @@
         <v>20.8</v>
       </c>
       <c r="V29" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W29" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X29" t="n">
         <v>4.4</v>
@@ -5641,7 +5708,7 @@
         <v>5.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA29" t="n">
         <v>20.6</v>
@@ -5650,13 +5717,13 @@
         <v>104.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF29" t="n">
         <v>10</v>
@@ -5671,7 +5738,7 @@
         <v>10</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK29" t="n">
         <v>14</v>
@@ -5686,13 +5753,13 @@
         <v>13</v>
       </c>
       <c r="AO29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ29" t="n">
         <v>3</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>2</v>
       </c>
       <c r="AR29" t="n">
         <v>15</v>
@@ -5707,10 +5774,10 @@
         <v>21</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX29" t="n">
         <v>22</v>
@@ -5719,16 +5786,16 @@
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AE30" t="n">
         <v>18</v>
@@ -5865,13 +5932,13 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO30" t="n">
         <v>16</v>
       </c>
       <c r="AP30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ30" t="n">
         <v>26</v>
@@ -5883,19 +5950,19 @@
         <v>18</v>
       </c>
       <c r="AT30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV30" t="n">
         <v>26</v>
       </c>
       <c r="AW30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY30" t="n">
         <v>12</v>
@@ -5907,7 +5974,7 @@
         <v>24</v>
       </c>
       <c r="BB30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC30" t="n">
         <v>17</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E31" t="n">
         <v>40</v>
       </c>
       <c r="F31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>0.571</v>
+        <v>0.58</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
       </c>
       <c r="I31" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J31" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K31" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
@@ -5969,13 +6036,13 @@
         <v>16.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="O31" t="n">
         <v>15.8</v>
       </c>
       <c r="P31" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q31" t="n">
         <v>0.744</v>
@@ -5984,13 +6051,13 @@
         <v>10.4</v>
       </c>
       <c r="S31" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="T31" t="n">
         <v>43.9</v>
       </c>
       <c r="U31" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="V31" t="n">
         <v>15</v>
@@ -6002,7 +6069,7 @@
         <v>4.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z31" t="n">
         <v>21</v>
@@ -6011,19 +6078,19 @@
         <v>19.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.5</v>
+        <v>98.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
       </c>
       <c r="AF31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG31" t="n">
         <v>12</v>
@@ -6035,7 +6102,7 @@
         <v>8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK31" t="n">
         <v>3</v>
@@ -6047,7 +6114,7 @@
         <v>27</v>
       </c>
       <c r="AN31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO31" t="n">
         <v>27</v>
@@ -6059,13 +6126,13 @@
         <v>20</v>
       </c>
       <c r="AR31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS31" t="n">
         <v>9</v>
       </c>
       <c r="AT31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU31" t="n">
         <v>6</v>
@@ -6074,13 +6141,13 @@
         <v>23</v>
       </c>
       <c r="AW31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
         <v>18</v>
@@ -6089,7 +6156,7 @@
         <v>21</v>
       </c>
       <c r="BB31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-22-2014-15</t>
+          <t>2015-03-22</t>
         </is>
       </c>
     </row>
